--- a/reports/Debug-purgatory-20260104/For Winter Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260104/For Winter Ending (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -31,6 +31,9 @@
     <t>Rentals</t>
   </si>
   <si>
+    <t>The Board Room</t>
+  </si>
+  <si>
     <t>Expert Edge</t>
   </si>
   <si>
@@ -67,22 +70,64 @@
     <t>Events</t>
   </si>
   <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
     <t>Guest Services</t>
   </si>
   <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
     <t>Grounds Maintenance</t>
   </si>
   <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
+    <t>DMC Dgo Mtn Club</t>
+  </si>
+  <si>
     <t>account</t>
   </si>
   <si>
+    <t>T103</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
-    <t>T105</t>
-  </si>
-  <si>
-    <t>T100</t>
+    <t>T101</t>
   </si>
   <si>
     <t>department</t>
@@ -100,6 +145,9 @@
     <t>D3000</t>
   </si>
   <si>
+    <t>D4052</t>
+  </si>
+  <si>
     <t>D4053</t>
   </si>
   <si>
@@ -118,7 +166,7 @@
     <t>D5202</t>
   </si>
   <si>
-    <t xml:space="preserve">D5205                    </t>
+    <t>D5205</t>
   </si>
   <si>
     <t>D5206</t>
@@ -136,10 +184,46 @@
     <t>D5810</t>
   </si>
   <si>
-    <t xml:space="preserve">D6720                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">D6780                    </t>
+    <t>D5820</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8810</t>
   </si>
   <si>
     <t>revenue</t>
@@ -505,13 +589,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -519,27 +602,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
       <c r="D2" s="2">
-        <v>2269.9700</v>
+        <v>780.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -547,13 +624,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D3" s="2">
-        <v>35090.0000</v>
+        <v>40095.00</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -561,217 +638,427 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2">
-        <v>3159685.9300</v>
+        <v>35206.00</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2">
-        <v>821527.8400</v>
+        <v>3160338.31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2">
-        <v>20880.0000</v>
+        <v>2269.97</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2">
-        <v>923296.6000</v>
+        <v>1263.50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2">
-        <v>82679.6400</v>
+        <v>2159488.38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2">
-        <v>405899.6300</v>
+        <v>824615.80</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2">
-        <v>142575.8800</v>
+        <v>22480.00</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2">
-        <v>119546.6300</v>
+        <v>943766.60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2">
-        <v>175622.7100</v>
+        <v>2.00</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2">
-        <v>193775.0100</v>
+        <v>98517.90</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D14" s="2">
-        <v>23668.8000</v>
+        <v>508299.42</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2">
-        <v>11878.0800</v>
+        <v>184865.05</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D16" s="2">
-        <v>102670.2700</v>
+        <v>140146.82</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2">
-        <v>482412.3000</v>
+        <v>196986.67</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2">
-        <v>79208.3500</v>
+        <v>207902.00</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2">
-        <v>1670.0000</v>
+        <v>24187.90</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2">
-        <v>27765.0000</v>
+        <v>47191.04</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2">
-        <v>2720.0000</v>
+        <v>116660.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="2">
+        <v>606194.52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="2">
+        <v>89479.92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="2">
+        <v>48830.00</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="2">
+        <v>300.00</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1574508.34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="2">
+        <v>139078.73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="2">
+        <v>85621.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="2">
+        <v>426925.66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="2">
+        <v>20872.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="2">
+        <v>58664.31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="2">
+        <v>190924.23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="2">
+        <v>124162.42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="2">
+        <v>127035.91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="2">
+        <v>21475.45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="2">
+        <v>8000.00</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="2">
+        <v>107184.63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1364.14</v>
       </c>
     </row>
   </sheetData>
